--- a/templates/base-table-sample.xlsx
+++ b/templates/base-table-sample.xlsx
@@ -8376,7 +8376,7 @@
       <formula1>"网页,图片,视频,新闻,Discover,Google 新闻"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"电脑,手机,平板"</formula1>
+      <formula1>"电脑,手机,平板,不区分（Discover 不给设备）"</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"初步,定稿"</formula1>
@@ -8731,7 +8731,7 @@
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>不允许空；Google 判断不出国家时写 ZZZ（未知）。</t>
+          <t>不允许空。Google 判断不出国家时写「未知（Google 判断不出国家）」；对照表里没有的国家代码原样写大写三字母。</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>搜索时用的是电脑、手机还是平板。</t>
+          <t>搜索时用的是电脑、手机还是平板。Discover 的数据 Google 不按设备拆分，这类行写「不区分（Discover 不给设备）」。</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>电脑；手机；平板</t>
+          <t>电脑；手机；平板；不区分（Discover 不给设备）</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9560,7 +9560,7 @@
       <formula1>"英文,德文"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"网页,图片,视频,新闻,Google 新闻"</formula1>
+      <formula1>"网页,图片,视频,新闻"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"电脑,手机,平板"</formula1>
@@ -9654,7 +9654,7 @@
     <row r="10" ht="37.5" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>这张表加起来比「网页表现」少是正常的：Google 为保护隐私不给出很少人搜的词，按搜索词细分时还会丢掉一部分行。看总数用网页表现，看具体是哪些词用这张。Discover 没有搜索词，所以这里没有 Discover 的行。</t>
+          <t>这张表加起来比「网页表现」少是正常的：Google 为保护隐私不给出很少人搜的词，按搜索词细分时还会丢掉一部分行。看总数用网页表现，看具体是哪些词用这张。Discover 和 Google 新闻 Google 不给搜索词，所以这里没有这两类的行，要看去「网页表现」。</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>在 Google 的哪种搜索里被看到：网页、图片、视频、新闻、Discover（手机 Google 首页推荐）、Google 新闻。</t>
+          <t>在 Google 的哪种搜索里被看到：网页、图片、视频、新闻。Discover 和 Google 新闻 Google 不给搜索词，所以这张表没有这两类。</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>网页；图片；视频；新闻；Google 新闻</t>
+          <t>网页；图片；视频；新闻</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>不允许空；Google 判断不出国家时写 ZZZ（未知）。</t>
+          <t>不允许空。Google 判断不出国家时写「未知（Google 判断不出国家）」；对照表里没有的国家代码原样写大写三字母。</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>

--- a/templates/base-table-sample.xlsx
+++ b/templates/base-table-sample.xlsx
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>订单的账单公司名；姓名、邮箱、电话、地址读到后立即丢弃，不进表。</t>
+          <t>订单的账单公司名；姓名、邮箱、电话、地址、IP、浏览器标识读到后立即丢弃，不进表。</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
